--- a/data/trans_dic/P42-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P42-Provincia-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>78,94%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>85,03%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,19; 83,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,79; 91,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,61; 88,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,52; 97,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,29; 83,81</t>
+          <t>73,19; 83,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,97; 91,98</t>
+          <t>83,79; 91,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,5; 88,67</t>
+          <t>80,61; 88,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,26; 97,23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73,29; 83,81</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83,97; 91,98</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80,5; 88,67</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,26; 97,23</t>
+          <t>84,52; 97,24</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>81,63%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>90,53%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78,09; 84,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,93; 93,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,64; 87,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,6; 93,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,92; 84,93</t>
+          <t>78,09; 84,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,79; 92,99</t>
+          <t>87,93; 93,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,57; 87,59</t>
+          <t>80,64; 87,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,38; 93,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77,92; 84,93</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>87,79; 92,99</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>80,57; 87,59</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,38; 93,12</t>
+          <t>86,6; 93,15</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86,64%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,14%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,29; 80,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,42; 89,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,22; 90,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,73; 85,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,03; 80,3</t>
+          <t>71,29; 80,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,14; 88,9</t>
+          <t>81,42; 89,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,3; 90,01</t>
+          <t>82,22; 90,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,95; 84,53</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>71,03; 80,3</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>81,14; 88,9</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82,3; 90,01</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>74,95; 84,53</t>
+          <t>74,73; 85,08</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>91,71%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,19; 80,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,68; 87,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,68; 88,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,69; 95,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,77; 80,42</t>
+          <t>72,19; 80,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,19; 87,85</t>
+          <t>80,68; 87,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,89; 88,29</t>
+          <t>80,68; 88,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,48; 95,67</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71,77; 80,42</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80,19; 87,85</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80,89; 88,29</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,48; 95,67</t>
+          <t>86,69; 95,9</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>86,42%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,82; 79,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,11; 89,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,36; 93,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,18; 89,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,33; 79,16</t>
+          <t>66,82; 79,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,32; 90,06</t>
+          <t>80,11; 89,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 93,2</t>
+          <t>85,36; 93,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80,99; 90,59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67,33; 79,16</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>80,32; 90,06</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>85,05; 93,2</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>80,99; 90,59</t>
+          <t>81,18; 89,86</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>70,53%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>70,53%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,19; 78,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,11; 89,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,61; 83,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,19; 75,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,67; 78,75</t>
+          <t>68,19; 78,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,49; 89,68</t>
+          <t>81,11; 89,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,99; 83,31</t>
+          <t>73,61; 83,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,56; 76,02</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>68,67; 78,75</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81,49; 89,68</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72,99; 83,31</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>64,56; 76,02</t>
+          <t>65,19; 75,65</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>59,94%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,94%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,64; 86,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,13; 91,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,1; 93,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,41; 88,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,64; 86,53</t>
+          <t>80,64; 86,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,95; 91,83</t>
+          <t>87,13; 91,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3; 93,85</t>
+          <t>89,1; 93,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,72; 88,29</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>80,64; 86,53</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>86,95; 91,83</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89,3; 93,85</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,72; 88,29</t>
+          <t>26,41; 88,16</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>85,14%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>77,78%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,82; 82,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,58; 87,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,44; 91,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,15; 80,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,97; 82,67</t>
+          <t>76,82; 82,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,54; 87,57</t>
+          <t>82,58; 87,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,36; 91,69</t>
+          <t>87,44; 91,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,51; 81,18</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>76,97; 82,67</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>82,54; 87,57</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>87,36; 91,69</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>74,51; 81,18</t>
+          <t>74,15; 80,97</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1413,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,26 +1447,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>78,55%</t>
         </is>
@@ -1837,62 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77,74; 80,45</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,08; 88,28</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,12; 88,42</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59,58; 85,19</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>77,74; 80,45</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>86,08; 88,28</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>86,12; 88,42</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>59,58; 85,19</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
     </row>
@@ -1904,17 +1508,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
@@ -1929,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1942,22 +1545,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,20 +1564,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2019,26 +1610,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -2055,10 +1626,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2073,22 +1640,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2107,26 +1674,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
@@ -2141,22 +1688,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205897</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250891</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2175,26 +1722,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>174526</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>205897</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>250891</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>239486</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>174526</t>
         </is>
@@ -2209,62 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>190919; 218322</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>238067; 260644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>227034; 249742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>157392; 181083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>191166; 218598</t>
+          <t>190919; 218322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>238584; 261337</t>
+          <t>238067; 260644</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>226723; 249742</t>
+          <t>227034; 249742</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>153186; 181063</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>191166; 218598</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>238584; 261337</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>226723; 249742</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>153186; 181063</t>
+          <t>157392; 181083</t>
         </is>
       </c>
     </row>
@@ -2281,22 +1788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2315,26 +1822,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>520</t>
         </is>
@@ -2349,22 +1836,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>409655</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474163</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>437523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2383,26 +1870,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367710</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>409655</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>474163</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>437523</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>367710</t>
         </is>
@@ -2417,62 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>391931; 425958</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>459693; 486897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>418697; 453440</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>351742; 378328</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>391053; 426218</t>
+          <t>391931; 425958</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>458960; 486119</t>
+          <t>459693; 486897</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>418316; 454791</t>
+          <t>418697; 453440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>350817; 378220</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>391053; 426218</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>458960; 486119</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>418316; 454791</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>350817; 378220</t>
+          <t>351742; 378328</t>
         </is>
       </c>
     </row>
@@ -2489,22 +1936,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2523,26 +1970,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2557,22 +1984,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253495</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>201294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2591,26 +2018,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>201294</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>253495</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>290219</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>289659</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>201294</t>
         </is>
@@ -2625,62 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>237768; 267438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>276816; 303724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>274880; 301177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>187686; 213684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>236913; 267834</t>
+          <t>237768; 267438</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>275866; 302247</t>
+          <t>276816; 303724</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>275149; 300924</t>
+          <t>274880; 301177</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>188238; 212315</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>236913; 267834</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>275866; 302247</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>275149; 300924</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>188238; 212315</t>
+          <t>187686; 213684</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2084,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>290</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2731,26 +2118,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>424</t>
         </is>
@@ -2765,22 +2132,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283040</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327986</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2799,26 +2166,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>353337</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>283040</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>327986</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>327054</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>353337</t>
         </is>
@@ -2833,62 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>267337; 298278</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>313032; 341144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>311711; 341522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>333962; 369450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>265797; 297841</t>
+          <t>267337; 298278</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>311119; 340839</t>
+          <t>313032; 341144</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>312523; 341115</t>
+          <t>311711; 341522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>333154; 368591</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>265797; 297841</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>311119; 340839</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>312523; 341115</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>333154; 368591</t>
+          <t>333962; 369450</t>
         </is>
       </c>
     </row>
@@ -2905,22 +2232,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2939,26 +2266,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
@@ -2973,22 +2280,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149214</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188207</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3007,26 +2314,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>131587</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>149214</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>188207</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>195122</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>131587</t>
         </is>
@@ -3041,62 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>135897; 161578</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>175921; 197068</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>185847; 202570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>123609; 136817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136931; 160989</t>
+          <t>135897; 161578</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>176368; 197754</t>
+          <t>175921; 197068</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185177; 202917</t>
+          <t>185847; 202570</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123311; 137934</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>136931; 160989</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>176368; 197754</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>185177; 202917</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>123311; 137934</t>
+          <t>123609; 136817</t>
         </is>
       </c>
     </row>
@@ -3113,22 +2380,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3147,26 +2414,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>288</t>
         </is>
@@ -3181,22 +2428,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204025</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241176</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3215,26 +2462,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>147981</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>204025</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>241176</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>214730</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>147981</t>
         </is>
@@ -3249,62 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>188865; 217036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>227138; 251830</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>201040; 227402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>136780; 158736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>190197; 218122</t>
+          <t>188865; 217036</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>228199; 251124</t>
+          <t>227138; 251830</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>199347; 227533</t>
+          <t>201040; 227402</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>135463; 159513</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>190197; 218122</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>228199; 251124</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>199347; 227533</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>135463; 159513</t>
+          <t>136780; 158736</t>
         </is>
       </c>
     </row>
@@ -3321,22 +2528,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>519</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>563</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3355,26 +2562,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>599</t>
         </is>
@@ -3389,22 +2576,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>534297</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>619193</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>628556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393933</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3423,26 +2610,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>393933</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>534297</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>619193</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>628556</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>393933</t>
         </is>
@@ -3457,62 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>514651; 551646</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>601833; 634631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>610220; 642488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>173554; 579370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>514690; 552259</t>
+          <t>514651; 551646</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>600581; 634287</t>
+          <t>601833; 634631</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>611538; 642752</t>
+          <t>610220; 642488</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>169024; 580252</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>514690; 552259</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>600581; 634287</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>611538; 642752</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>169024; 580252</t>
+          <t>173554; 579370</t>
         </is>
       </c>
     </row>
@@ -3529,22 +2676,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>590</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>635</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3563,26 +2710,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>701</t>
         </is>
@@ -3597,22 +2724,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621731</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691366</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>734423</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3631,26 +2758,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>449745</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>621731</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>691366</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>734423</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>449745</t>
         </is>
@@ -3665,62 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>598361; 643566</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>670582; 710006</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>716925; 752299</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>428759; 468209</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>599563; 643994</t>
+          <t>598361; 643566</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>670235; 711059</t>
+          <t>670582; 710006</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>716259; 751697</t>
+          <t>716925; 752299</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>430821; 469402</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>599563; 643994</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>670235; 711059</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>716259; 751697</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>430821; 469402</t>
+          <t>428759; 468209</t>
         </is>
       </c>
     </row>
@@ -3737,22 +2824,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3771,26 +2858,6 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>3520</t>
         </is>
@@ -3805,22 +2872,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3083200</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3066554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2220114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3839,26 +2906,6 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2220114</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3083200</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3066554</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>2220114</t>
         </is>
@@ -3873,62 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2615119; 2706419</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3044776; 3122790</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3028943; 3109819</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1683901; 2407647</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2615119; 2706419</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>3044776; 3122790</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>3028943; 3109819</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1683901; 2407647</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
     </row>
@@ -3940,7 +2967,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3948,10 +2975,9 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P42-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P42-Provincia-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,19; 83,7</t>
+          <t>72,88; 83,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,79; 91,74</t>
+          <t>83,68; 91,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,61; 88,67</t>
+          <t>80,48; 89,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,52; 97,24</t>
+          <t>89,6; 97,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,19; 83,7</t>
+          <t>72,88; 83,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,79; 91,74</t>
+          <t>83,68; 91,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,61; 88,67</t>
+          <t>80,48; 89,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,52; 97,24</t>
+          <t>89,6; 97,08</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,09; 84,87</t>
+          <t>77,95; 84,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,93; 93,14</t>
+          <t>87,78; 92,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,64; 87,33</t>
+          <t>80,82; 87,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,6; 93,15</t>
+          <t>85,91; 92,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,09; 84,87</t>
+          <t>77,95; 84,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,93; 93,14</t>
+          <t>87,78; 92,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,64; 87,33</t>
+          <t>80,82; 87,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,6; 93,15</t>
+          <t>85,91; 92,46</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,29; 80,18</t>
+          <t>71,01; 80,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,42; 89,34</t>
+          <t>81,39; 89,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,22; 90,09</t>
+          <t>82,6; 90,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,73; 85,08</t>
+          <t>74,82; 84,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,29; 80,18</t>
+          <t>71,01; 80,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,42; 89,34</t>
+          <t>81,39; 89,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,22; 90,09</t>
+          <t>82,6; 90,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,73; 85,08</t>
+          <t>74,82; 84,8</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 80,54</t>
+          <t>71,36; 80,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 87,93</t>
+          <t>80,23; 88,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 88,39</t>
+          <t>80,76; 88,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,69; 95,9</t>
+          <t>82,91; 92,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 80,54</t>
+          <t>71,36; 80,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 87,93</t>
+          <t>80,23; 88,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 88,39</t>
+          <t>80,76; 88,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,69; 95,9</t>
+          <t>82,91; 92,1</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,82; 79,45</t>
+          <t>67,09; 78,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,11; 89,74</t>
+          <t>80,58; 90,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,36; 93,04</t>
+          <t>85,19; 93,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,18; 89,86</t>
+          <t>80,07; 89,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,82; 79,45</t>
+          <t>67,09; 78,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,11; 89,74</t>
+          <t>80,58; 90,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,36; 93,04</t>
+          <t>85,19; 93,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>81,18; 89,86</t>
+          <t>80,07; 89,78</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,19; 78,36</t>
+          <t>67,88; 78,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,11; 89,93</t>
+          <t>81,42; 89,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,61; 83,26</t>
+          <t>73,61; 83,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,19; 75,65</t>
+          <t>66,09; 76,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,19; 78,36</t>
+          <t>67,88; 78,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,11; 89,93</t>
+          <t>81,42; 89,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,61; 83,26</t>
+          <t>73,61; 83,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,19; 75,65</t>
+          <t>66,09; 76,55</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,64; 86,44</t>
+          <t>80,64; 86,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,13; 91,88</t>
+          <t>86,94; 91,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,1; 93,81</t>
+          <t>89,35; 93,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 88,16</t>
+          <t>83,58; 90,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,64; 86,44</t>
+          <t>80,64; 86,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,13; 91,88</t>
+          <t>86,94; 91,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,1; 93,81</t>
+          <t>89,35; 93,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 88,16</t>
+          <t>83,58; 90,04</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,82; 82,62</t>
+          <t>76,77; 82,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,58; 87,44</t>
+          <t>82,59; 87,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87,44; 91,76</t>
+          <t>87,46; 91,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,15; 80,97</t>
+          <t>72,46; 79,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,82; 82,62</t>
+          <t>76,77; 82,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,58; 87,44</t>
+          <t>82,59; 87,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,44; 91,76</t>
+          <t>87,46; 91,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,15; 80,97</t>
+          <t>72,46; 79,45</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -1461,42 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174526</t>
+          <t>192811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>174526</t>
+          <t>192811</t>
         </is>
       </c>
     </row>
@@ -1736,42 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>190919; 218322</t>
+          <t>190103; 217944</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>238067; 260644</t>
+          <t>237761; 261183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>227034; 249742</t>
+          <t>226670; 250888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157392; 181083</t>
+          <t>182554; 197802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>190919; 218322</t>
+          <t>190103; 217944</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>238067; 260644</t>
+          <t>237761; 261183</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>227034; 249742</t>
+          <t>226670; 250888</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>157392; 181083</t>
+          <t>182554; 197802</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367710</t>
+          <t>387540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>367710</t>
+          <t>387540</t>
         </is>
       </c>
     </row>
@@ -1884,42 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>391931; 425958</t>
+          <t>391222; 425245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>459693; 486897</t>
+          <t>458910; 486007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>418697; 453440</t>
+          <t>419657; 454153</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>351742; 378328</t>
+          <t>370819; 399119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>391931; 425958</t>
+          <t>391222; 425245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>459693; 486897</t>
+          <t>458910; 486007</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>418697; 453440</t>
+          <t>419657; 454153</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>351742; 378328</t>
+          <t>370819; 399119</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>205331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>205331</t>
         </is>
       </c>
     </row>
@@ -2032,42 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>237768; 267438</t>
+          <t>236847; 267241</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>276816; 303724</t>
+          <t>276725; 303337</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>274880; 301177</t>
+          <t>276141; 301229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187686; 213684</t>
+          <t>191099; 216585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>237768; 267438</t>
+          <t>236847; 267241</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>276816; 303724</t>
+          <t>276725; 303337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>274880; 301177</t>
+          <t>276141; 301229</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>187686; 213684</t>
+          <t>191099; 216585</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353337</t>
+          <t>282580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>353337</t>
+          <t>282580</t>
         </is>
       </c>
     </row>
@@ -2180,42 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>267337; 298278</t>
+          <t>264272; 296293</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>313032; 341144</t>
+          <t>311274; 341655</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311711; 341522</t>
+          <t>312012; 340933</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>333962; 369450</t>
+          <t>265773; 295236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>267337; 298278</t>
+          <t>264272; 296293</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>313032; 341144</t>
+          <t>311274; 341655</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>311711; 341522</t>
+          <t>312012; 340933</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>333962; 369450</t>
+          <t>265773; 295236</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131587</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>131587</t>
+          <t>142451</t>
         </is>
       </c>
     </row>
@@ -2328,42 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>135897; 161578</t>
+          <t>136429; 160561</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>175921; 197068</t>
+          <t>176946; 197673</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185847; 202570</t>
+          <t>185483; 202925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123609; 136817</t>
+          <t>133330; 149494</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>135897; 161578</t>
+          <t>136429; 160561</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>175921; 197068</t>
+          <t>176946; 197673</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185847; 202570</t>
+          <t>185483; 202925</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123609; 136817</t>
+          <t>133330; 149494</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>153419</t>
         </is>
       </c>
     </row>
@@ -2476,42 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>188865; 217036</t>
+          <t>187997; 217592</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>227138; 251830</t>
+          <t>228005; 251466</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>201040; 227402</t>
+          <t>201051; 227428</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136780; 158736</t>
+          <t>142378; 164907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>188865; 217036</t>
+          <t>187997; 217592</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>227138; 251830</t>
+          <t>228005; 251466</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>201040; 227402</t>
+          <t>201051; 227428</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>136780; 158736</t>
+          <t>142378; 164907</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>468244</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>468244</t>
         </is>
       </c>
     </row>
@@ -2624,42 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>514651; 551646</t>
+          <t>514684; 551367</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>601833; 634631</t>
+          <t>600516; 634166</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>610220; 642488</t>
+          <t>611901; 642003</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>173554; 579370</t>
+          <t>447827; 482441</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>514651; 551646</t>
+          <t>514684; 551367</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>601833; 634631</t>
+          <t>600516; 634166</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>610220; 642488</t>
+          <t>611901; 642003</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>173554; 579370</t>
+          <t>447827; 482441</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>449745</t>
+          <t>511400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>449745</t>
+          <t>511400</t>
         </is>
       </c>
     </row>
@@ -2772,42 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>598361; 643566</t>
+          <t>598041; 643712</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>670582; 710006</t>
+          <t>670621; 710903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>716925; 752299</t>
+          <t>717087; 751340</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>428759; 468209</t>
+          <t>485975; 532796</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>598361; 643566</t>
+          <t>598041; 643712</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>670582; 710006</t>
+          <t>670621; 710903</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>716925; 752299</t>
+          <t>717087; 751340</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>428759; 468209</t>
+          <t>485975; 532796</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
     </row>
@@ -2920,42 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
     </row>
